--- a/informes_data/Segunda FEB/2025-26/playoffs/individual/NP_play_by_play_2512414_ELIMINATORIAS18FINAL_PROCESSED.xlsx
+++ b/informes_data/Segunda FEB/2025-26/playoffs/individual/NP_play_by_play_2512414_ELIMINATORIAS18FINAL_PROCESSED.xlsx
@@ -565,67 +565,67 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.4865</v>
+        <v>2.7435</v>
       </c>
       <c r="E2" t="n">
-        <v>0.3386</v>
+        <v>-0.5271</v>
       </c>
       <c r="F2" t="n">
-        <v>3.1479</v>
+        <v>3.2705</v>
       </c>
       <c r="G2" t="n">
-        <v>-1.4405</v>
+        <v>-1.3967</v>
       </c>
       <c r="H2" t="n">
-        <v>-1.8525</v>
+        <v>-1.7826</v>
       </c>
       <c r="I2" t="n">
-        <v>0.4119</v>
+        <v>0.386</v>
       </c>
       <c r="J2" t="n">
-        <v>-1.5267</v>
+        <v>-1.4274</v>
       </c>
       <c r="K2" t="n">
-        <v>-1.6848</v>
+        <v>-1.5864</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1581</v>
+        <v>0.159</v>
       </c>
       <c r="M2" t="n">
-        <v>0.0862</v>
+        <v>0.0307</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.1677</v>
+        <v>-0.1962</v>
       </c>
       <c r="O2" t="n">
-        <v>0.2539</v>
+        <v>0.2269</v>
       </c>
       <c r="P2" t="n">
-        <v>-1.8436</v>
+        <v>-1.8221</v>
       </c>
       <c r="Q2" t="n">
-        <v>-4.3018</v>
+        <v>-4.2515</v>
       </c>
       <c r="R2" t="n">
-        <v>2.4582</v>
+        <v>2.4294</v>
       </c>
       <c r="S2" t="n">
-        <v>2.2725</v>
+        <v>1.4136</v>
       </c>
       <c r="T2" t="n">
-        <v>1.5509</v>
+        <v>0.4842</v>
       </c>
       <c r="U2" t="n">
-        <v>0.7216</v>
+        <v>0.9294</v>
       </c>
       <c r="V2" t="n">
-        <v>4.4982</v>
+        <v>4.5485</v>
       </c>
       <c r="W2" t="n">
-        <v>4.6162</v>
+        <v>4.6676</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.1181</v>
+        <v>-0.119</v>
       </c>
     </row>
     <row r="3">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.612</v>
+        <v>1.871</v>
       </c>
       <c r="E3" t="n">
-        <v>-1.2152</v>
+        <v>-0.5676</v>
       </c>
       <c r="F3" t="n">
-        <v>2.8273</v>
+        <v>2.4386</v>
       </c>
       <c r="G3" t="n">
-        <v>1.8016</v>
+        <v>1.8069</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.8751</v>
+        <v>-0.87</v>
       </c>
       <c r="I3" t="n">
-        <v>2.6767</v>
+        <v>2.6769</v>
       </c>
       <c r="J3" t="n">
-        <v>1.3302</v>
+        <v>1.4024</v>
       </c>
       <c r="K3" t="n">
-        <v>-1.0697</v>
+        <v>-1.0299</v>
       </c>
       <c r="L3" t="n">
-        <v>2.3999</v>
+        <v>2.4323</v>
       </c>
       <c r="M3" t="n">
-        <v>0.4713</v>
+        <v>0.4046</v>
       </c>
       <c r="N3" t="n">
-        <v>0.1946</v>
+        <v>0.1599</v>
       </c>
       <c r="O3" t="n">
-        <v>0.2768</v>
+        <v>0.2446</v>
       </c>
       <c r="P3" t="n">
-        <v>-1.8436</v>
+        <v>-1.8221</v>
       </c>
       <c r="Q3" t="n">
-        <v>-4.3018</v>
+        <v>-4.2515</v>
       </c>
       <c r="R3" t="n">
-        <v>2.4582</v>
+        <v>2.4294</v>
       </c>
       <c r="S3" t="n">
-        <v>0.8336</v>
+        <v>1.0659</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.6048</v>
+        <v>-0.0989</v>
       </c>
       <c r="U3" t="n">
-        <v>1.4385</v>
+        <v>1.1648</v>
       </c>
       <c r="V3" t="n">
-        <v>0.8205</v>
+        <v>0.8202</v>
       </c>
       <c r="W3" t="n">
-        <v>2.3612</v>
+        <v>2.3804</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.5407</v>
+        <v>-1.5602</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>R. BLAK MOLLER</t>
+          <t>D. ORRIT SERRANO</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.5747</v>
+        <v>1.0474</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.4723</v>
+        <v>0.1047</v>
       </c>
       <c r="F4" t="n">
-        <v>1.047</v>
+        <v>0.9427</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.2782</v>
+        <v>1.9989</v>
       </c>
       <c r="H4" t="n">
-        <v>-1.5719</v>
+        <v>0.5926</v>
       </c>
       <c r="I4" t="n">
-        <v>1.2937</v>
+        <v>1.4062</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.514</v>
+        <v>2.7229</v>
       </c>
       <c r="K4" t="n">
-        <v>-1.739</v>
+        <v>0.887</v>
       </c>
       <c r="L4" t="n">
-        <v>1.225</v>
+        <v>1.836</v>
       </c>
       <c r="M4" t="n">
-        <v>0.2358</v>
+        <v>-0.7241</v>
       </c>
       <c r="N4" t="n">
-        <v>0.1671</v>
+        <v>-0.2943</v>
       </c>
       <c r="O4" t="n">
-        <v>0.0687</v>
+        <v>-0.4297</v>
       </c>
       <c r="P4" t="n">
-        <v>0.8194</v>
+        <v>-0.4049</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.2048</v>
+        <v>-2.0245</v>
       </c>
       <c r="R4" t="n">
-        <v>1.0242</v>
+        <v>1.6196</v>
       </c>
       <c r="S4" t="n">
-        <v>0.3937</v>
+        <v>0.0485</v>
       </c>
       <c r="T4" t="n">
-        <v>0.2466</v>
+        <v>-0.5937</v>
       </c>
       <c r="U4" t="n">
-        <v>0.147</v>
+        <v>0.6422</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.3601</v>
+        <v>-0.5951</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.3601</v>
+        <v>-0.5951</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>O. SIMA FATTY</t>
+          <t>S. ROMERO SANCHEZ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.397</v>
+        <v>0.994</v>
       </c>
       <c r="E5" t="n">
-        <v>1.1264</v>
+        <v>1.349</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.7294</v>
+        <v>-0.3549</v>
       </c>
       <c r="G5" t="n">
-        <v>-1.103</v>
+        <v>0.5089</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.1589</v>
+        <v>0.4351</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.9442</v>
+        <v>0.0737</v>
       </c>
       <c r="J5" t="n">
-        <v>0.3385</v>
+        <v>1.0343</v>
       </c>
       <c r="K5" t="n">
-        <v>0.2595</v>
+        <v>0.3747</v>
       </c>
       <c r="L5" t="n">
-        <v>0.079</v>
+        <v>0.6596</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.4415</v>
+        <v>-0.5254</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.4183</v>
+        <v>0.0605</v>
       </c>
       <c r="O5" t="n">
-        <v>-1.0232</v>
+        <v>-0.5859</v>
       </c>
       <c r="P5" t="n">
-        <v>0.2048</v>
+        <v>1.0123</v>
       </c>
       <c r="Q5" t="n">
+        <v>-0.2025</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1.2147</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0.6631</v>
+      </c>
+      <c r="T5" t="n">
+        <v>0.5172</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0.146</v>
+      </c>
+      <c r="V5" t="n">
+        <v>-1.1902</v>
+      </c>
+      <c r="W5" t="n">
         <v>0</v>
       </c>
-      <c r="R5" t="n">
-        <v>0.2048</v>
-      </c>
-      <c r="S5" t="n">
-        <v>0.8110000000000001</v>
-      </c>
-      <c r="T5" t="n">
-        <v>0.3038</v>
-      </c>
-      <c r="U5" t="n">
-        <v>0.5073</v>
-      </c>
-      <c r="V5" t="n">
-        <v>0.4841</v>
-      </c>
-      <c r="W5" t="n">
-        <v>0.4841</v>
-      </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-1.1902</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>S. ROMERO SANCHEZ</t>
+          <t>R. BLAK MOLLER</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.2469</v>
+        <v>0.7009</v>
       </c>
       <c r="E6" t="n">
-        <v>0.7181</v>
+        <v>-0.4365</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.4712</v>
+        <v>1.1374</v>
       </c>
       <c r="G6" t="n">
-        <v>0.5276999999999999</v>
+        <v>-0.2766</v>
       </c>
       <c r="H6" t="n">
-        <v>0.4403</v>
+        <v>-1.5621</v>
       </c>
       <c r="I6" t="n">
-        <v>0.08740000000000001</v>
+        <v>1.2855</v>
       </c>
       <c r="J6" t="n">
-        <v>1.0038</v>
+        <v>-0.4883</v>
       </c>
       <c r="K6" t="n">
-        <v>0.3571</v>
+        <v>-1.7207</v>
       </c>
       <c r="L6" t="n">
-        <v>0.6468</v>
+        <v>1.2324</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.4761</v>
+        <v>0.2117</v>
       </c>
       <c r="N6" t="n">
-        <v>0.0833</v>
+        <v>0.1586</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.5593</v>
+        <v>0.0531</v>
       </c>
       <c r="P6" t="n">
-        <v>1.0242</v>
+        <v>0.8098</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.2048</v>
+        <v>-0.2025</v>
       </c>
       <c r="R6" t="n">
-        <v>1.2291</v>
+        <v>1.0123</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.1244</v>
+        <v>0.5377</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.0809</v>
+        <v>0.2542</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.0436</v>
+        <v>0.2834</v>
       </c>
       <c r="V6" t="n">
-        <v>-1.1806</v>
+        <v>-0.37</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.1806</v>
+        <v>-0.37</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>D. ORRIT SERRANO</t>
+          <t>D. GUEYE</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.2381</v>
+        <v>-0.025</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.7141999999999999</v>
+        <v>2.8156</v>
       </c>
       <c r="F7" t="n">
-        <v>0.9523</v>
+        <v>-2.8406</v>
       </c>
       <c r="G7" t="n">
-        <v>1.9956</v>
+        <v>2.6949</v>
       </c>
       <c r="H7" t="n">
-        <v>0.5855</v>
+        <v>1.2651</v>
       </c>
       <c r="I7" t="n">
-        <v>1.4101</v>
+        <v>1.4297</v>
       </c>
       <c r="J7" t="n">
-        <v>2.6442</v>
+        <v>4.0685</v>
       </c>
       <c r="K7" t="n">
-        <v>0.837</v>
+        <v>1.6199</v>
       </c>
       <c r="L7" t="n">
-        <v>1.8072</v>
+        <v>2.4486</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.6486</v>
+        <v>-1.3736</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.2515</v>
+        <v>-0.3548</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.3971</v>
+        <v>-1.0188</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.4097</v>
+        <v>-0.8098</v>
       </c>
       <c r="Q7" t="n">
-        <v>-2.0485</v>
+        <v>-1.0123</v>
       </c>
       <c r="R7" t="n">
-        <v>1.6388</v>
+        <v>0.2025</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.7575</v>
+        <v>-0.218</v>
       </c>
       <c r="T7" t="n">
-        <v>-1.31</v>
+        <v>-0.2406</v>
       </c>
       <c r="U7" t="n">
-        <v>0.5524</v>
+        <v>0.0226</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.5903</v>
+        <v>-1.6921</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.5903</v>
+        <v>-1.6921</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>D. GUEYE</t>
+          <t>O. SIMA FATTY</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.0153</v>
+        <v>-0.211</v>
       </c>
       <c r="E8" t="n">
-        <v>2.5424</v>
+        <v>0.8537</v>
       </c>
       <c r="F8" t="n">
-        <v>-2.5271</v>
+        <v>-1.0648</v>
       </c>
       <c r="G8" t="n">
-        <v>2.6901</v>
+        <v>-1.1152</v>
       </c>
       <c r="H8" t="n">
-        <v>1.2654</v>
+        <v>-0.1582</v>
       </c>
       <c r="I8" t="n">
-        <v>1.4246</v>
+        <v>-0.957</v>
       </c>
       <c r="J8" t="n">
-        <v>4.0252</v>
+        <v>0.3554</v>
       </c>
       <c r="K8" t="n">
-        <v>1.6002</v>
+        <v>0.2759</v>
       </c>
       <c r="L8" t="n">
-        <v>2.4249</v>
+        <v>0.0795</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.3351</v>
+        <v>-1.4706</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.3348</v>
+        <v>-0.4341</v>
       </c>
       <c r="O8" t="n">
-        <v>-1.0003</v>
+        <v>-1.0365</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.8194</v>
+        <v>0.2025</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.0242</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>0.2048</v>
+        <v>0.2025</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.1906</v>
+        <v>0.1999</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.4585</v>
+        <v>-0.0035</v>
       </c>
       <c r="U8" t="n">
-        <v>0.2679</v>
+        <v>0.2034</v>
       </c>
       <c r="V8" t="n">
-        <v>-1.6647</v>
+        <v>0.5019</v>
       </c>
       <c r="W8" t="n">
+        <v>0.5019</v>
+      </c>
+      <c r="X8" t="n">
         <v>0</v>
-      </c>
-      <c r="X8" t="n">
-        <v>-1.6647</v>
       </c>
     </row>
     <row r="9">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.4518</v>
+        <v>-3.0293</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.1385</v>
+        <v>-2.5079</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.3133</v>
+        <v>-0.5214</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.1009</v>
+        <v>-1.1328</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.633</v>
+        <v>-0.6514</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.4679</v>
+        <v>-0.4814</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.1736</v>
+        <v>-0.1319</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.2421</v>
+        <v>-0.2186</v>
       </c>
       <c r="L9" t="n">
-        <v>0.06850000000000001</v>
+        <v>0.0868</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.9273</v>
+        <v>-1.0009</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.3909</v>
+        <v>-0.4327</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.5364</v>
+        <v>-0.5682</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.2048</v>
+        <v>-0.2025</v>
       </c>
       <c r="Q9" t="n">
-        <v>-2.0485</v>
+        <v>-2.0245</v>
       </c>
       <c r="R9" t="n">
-        <v>1.8436</v>
+        <v>1.8221</v>
       </c>
       <c r="S9" t="n">
-        <v>0.9849</v>
+        <v>0.4612</v>
       </c>
       <c r="T9" t="n">
-        <v>0.08359999999999999</v>
+        <v>-0.3515</v>
       </c>
       <c r="U9" t="n">
-        <v>0.9014</v>
+        <v>0.8127</v>
       </c>
       <c r="V9" t="n">
-        <v>-2.131</v>
+        <v>-2.1553</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-2.131</v>
+        <v>-2.1553</v>
       </c>
     </row>
     <row r="10">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.9916</v>
+        <v>-3.6504</v>
       </c>
       <c r="E10" t="n">
-        <v>-5.3967</v>
+        <v>-5.0593</v>
       </c>
       <c r="F10" t="n">
-        <v>1.4052</v>
+        <v>1.4089</v>
       </c>
       <c r="G10" t="n">
-        <v>-4.1165</v>
+        <v>-4.1005</v>
       </c>
       <c r="H10" t="n">
-        <v>-3.3304</v>
+        <v>-3.3025</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.7861</v>
+        <v>-0.798</v>
       </c>
       <c r="J10" t="n">
-        <v>-2.604</v>
+        <v>-2.5258</v>
       </c>
       <c r="K10" t="n">
-        <v>-2.6331</v>
+        <v>-2.5728</v>
       </c>
       <c r="L10" t="n">
-        <v>0.029</v>
+        <v>0.047</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.5125</v>
+        <v>-1.5747</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.6973</v>
+        <v>-0.7297</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.8151</v>
+        <v>-0.845</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Q10" t="n">
-        <v>-2.2533</v>
+        <v>-2.227</v>
       </c>
       <c r="R10" t="n">
-        <v>2.2533</v>
+        <v>2.227</v>
       </c>
       <c r="S10" t="n">
-        <v>0.243</v>
+        <v>0.5692</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.5393</v>
+        <v>-0.3065</v>
       </c>
       <c r="U10" t="n">
-        <v>0.7824</v>
+        <v>0.8757</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.1181</v>
+        <v>-0.119</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.1181</v>
+        <v>-0.119</v>
       </c>
     </row>
     <row r="11">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>0.1270999999999995</v>
+        <v>0.4411</v>
       </c>
       <c r="E11" t="n">
-        <v>-5.211399999999999</v>
+        <v>-3.9754</v>
       </c>
       <c r="F11" t="n">
-        <v>5.3387</v>
+        <v>4.4164</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.0241</v>
+        <v>-1.0122</v>
       </c>
       <c r="H11" t="n">
-        <v>-6.1306</v>
+        <v>-6.034000000000001</v>
       </c>
       <c r="I11" t="n">
-        <v>5.1062</v>
+        <v>5.0216</v>
       </c>
       <c r="J11" t="n">
-        <v>4.5236</v>
+        <v>5.0101</v>
       </c>
       <c r="K11" t="n">
-        <v>-4.3149</v>
+        <v>-3.9709</v>
       </c>
       <c r="L11" t="n">
-        <v>8.8384</v>
+        <v>8.981200000000001</v>
       </c>
       <c r="M11" t="n">
-        <v>-5.547800000000001</v>
+        <v>-6.0223</v>
       </c>
       <c r="N11" t="n">
-        <v>-1.8155</v>
+        <v>-2.0628</v>
       </c>
       <c r="O11" t="n">
-        <v>-3.732</v>
+        <v>-3.959499999999999</v>
       </c>
       <c r="P11" t="n">
-        <v>-3.0727</v>
+        <v>-3.0368</v>
       </c>
       <c r="Q11" t="n">
-        <v>-16.3877</v>
+        <v>-16.1963</v>
       </c>
       <c r="R11" t="n">
-        <v>13.315</v>
+        <v>13.1595</v>
       </c>
       <c r="S11" t="n">
-        <v>4.466200000000001</v>
+        <v>4.7411</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.8086000000000001</v>
+        <v>-0.3391</v>
       </c>
       <c r="U11" t="n">
-        <v>5.2749</v>
+        <v>5.0802</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.2420000000000008</v>
+        <v>-0.2511000000000003</v>
       </c>
       <c r="W11" t="n">
-        <v>7.4615</v>
+        <v>7.5499</v>
       </c>
       <c r="X11" t="n">
-        <v>-7.7036</v>
+        <v>-7.8009</v>
       </c>
     </row>
     <row r="12">
@@ -1345,64 +1345,64 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>7.1803</v>
+        <v>7.4276</v>
       </c>
       <c r="E12" t="n">
-        <v>4.1398</v>
+        <v>3.9336</v>
       </c>
       <c r="F12" t="n">
-        <v>3.0405</v>
+        <v>3.494</v>
       </c>
       <c r="G12" t="n">
-        <v>2.4209</v>
+        <v>2.4302</v>
       </c>
       <c r="H12" t="n">
-        <v>2.9575</v>
+        <v>2.9647</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.5366</v>
+        <v>-0.5345</v>
       </c>
       <c r="J12" t="n">
-        <v>1.4657</v>
+        <v>1.5275</v>
       </c>
       <c r="K12" t="n">
-        <v>1.3971</v>
+        <v>1.4408</v>
       </c>
       <c r="L12" t="n">
-        <v>0.06850000000000001</v>
+        <v>0.0868</v>
       </c>
       <c r="M12" t="n">
-        <v>0.9552</v>
+        <v>0.9026999999999999</v>
       </c>
       <c r="N12" t="n">
-        <v>1.5603</v>
+        <v>1.5239</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.6051</v>
+        <v>-0.6213</v>
       </c>
       <c r="P12" t="n">
-        <v>2.4582</v>
+        <v>2.4294</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>2.4582</v>
+        <v>2.4294</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.6502</v>
+        <v>-0.4075</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.2774</v>
+        <v>-0.5695</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.3729</v>
+        <v>0.162</v>
       </c>
       <c r="V12" t="n">
-        <v>2.9515</v>
+        <v>2.9755</v>
       </c>
       <c r="W12" t="n">
-        <v>2.9515</v>
+        <v>2.9755</v>
       </c>
       <c r="X12" t="n">
         <v>0</v>
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>3.7739</v>
+        <v>3.5911</v>
       </c>
       <c r="E13" t="n">
-        <v>1.8242</v>
+        <v>1.5996</v>
       </c>
       <c r="F13" t="n">
-        <v>1.9497</v>
+        <v>1.9915</v>
       </c>
       <c r="G13" t="n">
-        <v>3.0956</v>
+        <v>3.0914</v>
       </c>
       <c r="H13" t="n">
-        <v>3.0852</v>
+        <v>3.065</v>
       </c>
       <c r="I13" t="n">
-        <v>0.0103</v>
+        <v>0.0264</v>
       </c>
       <c r="J13" t="n">
-        <v>2.5355</v>
+        <v>2.5862</v>
       </c>
       <c r="K13" t="n">
-        <v>1.3856</v>
+        <v>1.4026</v>
       </c>
       <c r="L13" t="n">
-        <v>1.15</v>
+        <v>1.1836</v>
       </c>
       <c r="M13" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.5051</v>
       </c>
       <c r="N13" t="n">
-        <v>1.6997</v>
+        <v>1.6624</v>
       </c>
       <c r="O13" t="n">
-        <v>-1.1396</v>
+        <v>-1.1572</v>
       </c>
       <c r="P13" t="n">
-        <v>1.4339</v>
+        <v>1.4172</v>
       </c>
       <c r="Q13" t="n">
-        <v>-1.0242</v>
+        <v>-1.0123</v>
       </c>
       <c r="R13" t="n">
-        <v>2.4582</v>
+        <v>2.4294</v>
       </c>
       <c r="S13" t="n">
-        <v>0.07679999999999999</v>
+        <v>-0.0713</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.2774</v>
+        <v>-0.5695</v>
       </c>
       <c r="U13" t="n">
-        <v>0.3541</v>
+        <v>0.4982</v>
       </c>
       <c r="V13" t="n">
-        <v>-0.8324</v>
+        <v>-0.846</v>
       </c>
       <c r="W13" t="n">
-        <v>0.5903</v>
+        <v>0.5951</v>
       </c>
       <c r="X13" t="n">
-        <v>-1.4227</v>
+        <v>-1.4411</v>
       </c>
     </row>
     <row r="14">
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.0767</v>
+        <v>1.7929</v>
       </c>
       <c r="E14" t="n">
-        <v>1.5722</v>
+        <v>2.0337</v>
       </c>
       <c r="F14" t="n">
-        <v>0.5044999999999999</v>
+        <v>-0.2407</v>
       </c>
       <c r="G14" t="n">
-        <v>4.2101</v>
+        <v>4.2385</v>
       </c>
       <c r="H14" t="n">
-        <v>1.7</v>
+        <v>1.6812</v>
       </c>
       <c r="I14" t="n">
-        <v>2.5101</v>
+        <v>2.5574</v>
       </c>
       <c r="J14" t="n">
-        <v>4.4635</v>
+        <v>4.565</v>
       </c>
       <c r="K14" t="n">
-        <v>0.5580000000000001</v>
+        <v>0.5913</v>
       </c>
       <c r="L14" t="n">
-        <v>3.9055</v>
+        <v>3.9737</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.2535</v>
+        <v>-0.3265</v>
       </c>
       <c r="N14" t="n">
-        <v>1.142</v>
+        <v>1.0899</v>
       </c>
       <c r="O14" t="n">
-        <v>-1.3954</v>
+        <v>-1.4164</v>
       </c>
       <c r="P14" t="n">
-        <v>0.4097</v>
+        <v>0.4049</v>
       </c>
       <c r="Q14" t="n">
-        <v>-1.0242</v>
+        <v>-1.0123</v>
       </c>
       <c r="R14" t="n">
-        <v>1.4339</v>
+        <v>1.4172</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.1818</v>
+        <v>-0.4701</v>
       </c>
       <c r="T14" t="n">
-        <v>-1.1706</v>
+        <v>-0.8308</v>
       </c>
       <c r="U14" t="n">
-        <v>0.9888</v>
+        <v>0.3607</v>
       </c>
       <c r="V14" t="n">
-        <v>-2.3612</v>
+        <v>-2.3804</v>
       </c>
       <c r="W14" t="n">
-        <v>-0.6965</v>
+        <v>-0.6883</v>
       </c>
       <c r="X14" t="n">
-        <v>-1.6647</v>
+        <v>-1.6921</v>
       </c>
     </row>
     <row r="15">
@@ -1579,58 +1579,58 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.5</v>
+        <v>0.9651</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.4304</v>
+        <v>-0.1941</v>
       </c>
       <c r="F15" t="n">
-        <v>0.9304</v>
+        <v>1.1592</v>
       </c>
       <c r="G15" t="n">
-        <v>0.241</v>
+        <v>0.2405</v>
       </c>
       <c r="H15" t="n">
-        <v>0.3845</v>
+        <v>0.376</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.1435</v>
+        <v>-0.1355</v>
       </c>
       <c r="J15" t="n">
-        <v>0.0281</v>
+        <v>0.0465</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.6187</v>
+        <v>-0.6131</v>
       </c>
       <c r="L15" t="n">
-        <v>0.6468</v>
+        <v>0.6596</v>
       </c>
       <c r="M15" t="n">
-        <v>0.2129</v>
+        <v>0.194</v>
       </c>
       <c r="N15" t="n">
-        <v>1.0032</v>
+        <v>0.9891</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.7903</v>
+        <v>-0.7951</v>
       </c>
       <c r="P15" t="n">
-        <v>0.8194</v>
+        <v>0.8098</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>0.8194</v>
+        <v>0.8098</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.5603</v>
+        <v>-0.0852</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.4585</v>
+        <v>-0.2406</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.1019</v>
+        <v>0.1554</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>B. VANACLOCHA SANCHEZ</t>
+          <t>V. AGUILAR HERNANDEZ</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,64 +1657,64 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.0411</v>
+        <v>-0.0277</v>
       </c>
       <c r="E16" t="n">
-        <v>0.7413</v>
+        <v>-4.6425</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.7002</v>
+        <v>4.6148</v>
       </c>
       <c r="G16" t="n">
-        <v>0.3647</v>
+        <v>1.0759</v>
       </c>
       <c r="H16" t="n">
-        <v>0.2814</v>
+        <v>2.4323</v>
       </c>
       <c r="I16" t="n">
-        <v>0.0832</v>
+        <v>-1.3563</v>
       </c>
       <c r="J16" t="n">
-        <v>1.8294</v>
+        <v>-0.4823</v>
       </c>
       <c r="K16" t="n">
-        <v>1.1181</v>
+        <v>0.9272</v>
       </c>
       <c r="L16" t="n">
-        <v>0.7113</v>
+        <v>-1.4095</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.4647</v>
+        <v>1.5582</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.8367</v>
+        <v>1.5051</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.628</v>
+        <v>0.0531</v>
       </c>
       <c r="P16" t="n">
-        <v>-1.2291</v>
+        <v>-1.2147</v>
       </c>
       <c r="Q16" t="n">
-        <v>-2.0485</v>
+        <v>-4.049</v>
       </c>
       <c r="R16" t="n">
-        <v>0.8194</v>
+        <v>2.8343</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.2751</v>
+        <v>-0.484</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.2202</v>
+        <v>-0.7063</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.0549</v>
+        <v>0.2223</v>
       </c>
       <c r="V16" t="n">
-        <v>1.1806</v>
+        <v>0.5951</v>
       </c>
       <c r="W16" t="n">
-        <v>1.1806</v>
+        <v>0.5951</v>
       </c>
       <c r="X16" t="n">
         <v>0</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>V. AGUILAR HERNANDEZ</t>
+          <t>B. VANACLOCHA SANCHEZ</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,64 +1735,64 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.0502</v>
+        <v>-0.1589</v>
       </c>
       <c r="E17" t="n">
-        <v>-4.8068</v>
+        <v>0.7181999999999999</v>
       </c>
       <c r="F17" t="n">
-        <v>4.7566</v>
+        <v>-0.8772</v>
       </c>
       <c r="G17" t="n">
-        <v>1.0645</v>
+        <v>0.3536</v>
       </c>
       <c r="H17" t="n">
-        <v>2.4498</v>
+        <v>0.277</v>
       </c>
       <c r="I17" t="n">
-        <v>-1.3853</v>
+        <v>0.0766</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.5642</v>
+        <v>1.8607</v>
       </c>
       <c r="K17" t="n">
-        <v>0.8898</v>
+        <v>1.1451</v>
       </c>
       <c r="L17" t="n">
-        <v>-1.454</v>
+        <v>0.7156</v>
       </c>
       <c r="M17" t="n">
-        <v>1.6287</v>
+        <v>-1.5071</v>
       </c>
       <c r="N17" t="n">
-        <v>1.56</v>
+        <v>-0.8682</v>
       </c>
       <c r="O17" t="n">
-        <v>0.0687</v>
+        <v>-0.639</v>
       </c>
       <c r="P17" t="n">
-        <v>-1.2291</v>
+        <v>-1.2147</v>
       </c>
       <c r="Q17" t="n">
-        <v>-4.097</v>
+        <v>-2.0245</v>
       </c>
       <c r="R17" t="n">
-        <v>2.8679</v>
+        <v>0.8098</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.4759</v>
+        <v>-0.488</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.7358</v>
+        <v>-0.3082</v>
       </c>
       <c r="U17" t="n">
-        <v>0.26</v>
+        <v>-0.1798</v>
       </c>
       <c r="V17" t="n">
-        <v>0.5903</v>
+        <v>1.1902</v>
       </c>
       <c r="W17" t="n">
-        <v>0.5903</v>
+        <v>1.1902</v>
       </c>
       <c r="X17" t="n">
         <v>0</v>
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.1361</v>
+        <v>-1.0364</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.3577</v>
+        <v>-1.3465</v>
       </c>
       <c r="F18" t="n">
-        <v>0.2216</v>
+        <v>0.3102</v>
       </c>
       <c r="G18" t="n">
-        <v>-2.2942</v>
+        <v>-2.3393</v>
       </c>
       <c r="H18" t="n">
-        <v>-1.4499</v>
+        <v>-1.481</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.8443000000000001</v>
+        <v>-0.8584000000000001</v>
       </c>
       <c r="J18" t="n">
-        <v>-1.1766</v>
+        <v>-1.1433</v>
       </c>
       <c r="K18" t="n">
-        <v>-1.3097</v>
+        <v>-1.2861</v>
       </c>
       <c r="L18" t="n">
-        <v>0.1331</v>
+        <v>0.1428</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.1176</v>
+        <v>-1.196</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.1402</v>
+        <v>-0.1949</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.9774</v>
+        <v>-1.0011</v>
       </c>
       <c r="P18" t="n">
-        <v>0.4097</v>
+        <v>0.4049</v>
       </c>
       <c r="Q18" t="n">
-        <v>-2.0485</v>
+        <v>-2.0245</v>
       </c>
       <c r="R18" t="n">
-        <v>2.4582</v>
+        <v>2.4294</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.0224</v>
+        <v>-0.8873</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.7358</v>
+        <v>-0.8101</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.2866</v>
+        <v>-0.0772</v>
       </c>
       <c r="V18" t="n">
-        <v>1.7709</v>
+        <v>1.7853</v>
       </c>
       <c r="W18" t="n">
-        <v>2.6033</v>
+        <v>2.6313</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.8324</v>
+        <v>-0.846</v>
       </c>
     </row>
     <row r="19">
@@ -1891,64 +1891,64 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.8384</v>
+        <v>-2.9304</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.5402</v>
+        <v>-1.5819</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.2982</v>
+        <v>-1.3485</v>
       </c>
       <c r="G19" t="n">
-        <v>-4.1297</v>
+        <v>-4.1209</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.2592</v>
+        <v>-0.2571</v>
       </c>
       <c r="I19" t="n">
-        <v>-3.8705</v>
+        <v>-3.8638</v>
       </c>
       <c r="J19" t="n">
-        <v>-1.824</v>
+        <v>-1.7808</v>
       </c>
       <c r="K19" t="n">
-        <v>0.884</v>
+        <v>0.9081</v>
       </c>
       <c r="L19" t="n">
-        <v>-2.708</v>
+        <v>-2.6889</v>
       </c>
       <c r="M19" t="n">
-        <v>-2.3057</v>
+        <v>-2.3401</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.1432</v>
+        <v>-1.1651</v>
       </c>
       <c r="O19" t="n">
-        <v>-1.1625</v>
+        <v>-1.1749</v>
       </c>
       <c r="P19" t="n">
-        <v>0.8194</v>
+        <v>0.8098</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>0.8194</v>
+        <v>0.8098</v>
       </c>
       <c r="S19" t="n">
-        <v>0.2299</v>
+        <v>0.1297</v>
       </c>
       <c r="T19" t="n">
-        <v>0.0418</v>
+        <v>-0.052</v>
       </c>
       <c r="U19" t="n">
-        <v>0.1881</v>
+        <v>0.1817</v>
       </c>
       <c r="V19" t="n">
-        <v>0.2421</v>
+        <v>0.2509</v>
       </c>
       <c r="W19" t="n">
-        <v>0.2421</v>
+        <v>0.2509</v>
       </c>
       <c r="X19" t="n">
         <v>0</v>
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-4.0521</v>
+        <v>-3.894</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.5902</v>
+        <v>-2.5294</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.4619</v>
+        <v>-1.3646</v>
       </c>
       <c r="G20" t="n">
-        <v>-2.065</v>
+        <v>-2.0649</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.6632</v>
+        <v>-0.6528</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.4017</v>
+        <v>-1.412</v>
       </c>
       <c r="J20" t="n">
-        <v>-1.1531</v>
+        <v>-1.1278</v>
       </c>
       <c r="K20" t="n">
-        <v>-1.1926</v>
+        <v>-1.1675</v>
       </c>
       <c r="L20" t="n">
-        <v>0.0395</v>
+        <v>0.0398</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.9119</v>
+        <v>-0.9371</v>
       </c>
       <c r="N20" t="n">
-        <v>0.5294</v>
+        <v>0.5147</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.4413</v>
+        <v>-1.4518</v>
       </c>
       <c r="P20" t="n">
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.0242</v>
+        <v>-1.0123</v>
       </c>
       <c r="R20" t="n">
-        <v>1.0242</v>
+        <v>1.0123</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.0486</v>
+        <v>-0.8898</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.655</v>
+        <v>-0.6403</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.3937</v>
+        <v>-0.2495</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.9385</v>
+        <v>-0.9393</v>
       </c>
       <c r="W20" t="n">
-        <v>0.2421</v>
+        <v>0.2509</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.1806</v>
+        <v>-1.1902</v>
       </c>
     </row>
     <row r="21">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-5.6226</v>
+        <v>-5.1583</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.8909</v>
+        <v>-2.4071</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.7317</v>
+        <v>-2.7512</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.8835</v>
+        <v>-1.8928</v>
       </c>
       <c r="H21" t="n">
-        <v>-2.3555</v>
+        <v>-2.3713</v>
       </c>
       <c r="I21" t="n">
-        <v>0.4721</v>
+        <v>0.4785</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.0565</v>
+        <v>-0.0295</v>
       </c>
       <c r="K21" t="n">
-        <v>-1.2959</v>
+        <v>-1.2854</v>
       </c>
       <c r="L21" t="n">
-        <v>1.2395</v>
+        <v>1.2559</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.827</v>
+        <v>-1.8633</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.0596</v>
+        <v>-1.0859</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.7674</v>
+        <v>-0.7774</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.8194</v>
+        <v>-0.8098</v>
       </c>
       <c r="Q21" t="n">
-        <v>-2.0485</v>
+        <v>-2.0245</v>
       </c>
       <c r="R21" t="n">
-        <v>1.2291</v>
+        <v>1.2147</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.5585</v>
+        <v>-0.07530000000000001</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.786</v>
+        <v>-0.3531</v>
       </c>
       <c r="U21" t="n">
-        <v>0.2274</v>
+        <v>0.2778</v>
       </c>
       <c r="V21" t="n">
-        <v>-2.3612</v>
+        <v>-2.3804</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-2.3612</v>
+        <v>-2.3804</v>
       </c>
     </row>
     <row r="22">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.1274000000000006</v>
+        <v>0.5709999999999971</v>
       </c>
       <c r="E22" t="n">
-        <v>-5.338699999999999</v>
+        <v>-4.4164</v>
       </c>
       <c r="F22" t="n">
-        <v>5.2113</v>
+        <v>4.987499999999999</v>
       </c>
       <c r="G22" t="n">
-        <v>1.024400000000001</v>
+        <v>1.0122</v>
       </c>
       <c r="H22" t="n">
-        <v>6.1306</v>
+        <v>6.034000000000001</v>
       </c>
       <c r="I22" t="n">
-        <v>-5.1062</v>
+        <v>-5.021599999999999</v>
       </c>
       <c r="J22" t="n">
-        <v>5.547799999999999</v>
+        <v>6.022200000000002</v>
       </c>
       <c r="K22" t="n">
-        <v>1.815700000000001</v>
+        <v>2.063</v>
       </c>
       <c r="L22" t="n">
-        <v>3.732199999999999</v>
+        <v>3.9594</v>
       </c>
       <c r="M22" t="n">
-        <v>-4.5236</v>
+        <v>-5.0101</v>
       </c>
       <c r="N22" t="n">
-        <v>4.3149</v>
+        <v>3.971000000000001</v>
       </c>
       <c r="O22" t="n">
-        <v>-8.8383</v>
+        <v>-8.981100000000001</v>
       </c>
       <c r="P22" t="n">
-        <v>3.0727</v>
+        <v>3.036799999999999</v>
       </c>
       <c r="Q22" t="n">
-        <v>-13.3151</v>
+        <v>-13.1594</v>
       </c>
       <c r="R22" t="n">
-        <v>16.3879</v>
+        <v>16.1961</v>
       </c>
       <c r="S22" t="n">
-        <v>-4.4661</v>
+        <v>-3.7288</v>
       </c>
       <c r="T22" t="n">
-        <v>-5.274900000000001</v>
+        <v>-5.0804</v>
       </c>
       <c r="U22" t="n">
-        <v>0.8084000000000002</v>
+        <v>1.3516</v>
       </c>
       <c r="V22" t="n">
-        <v>0.2420999999999993</v>
+        <v>0.2508999999999997</v>
       </c>
       <c r="W22" t="n">
-        <v>7.7037</v>
+        <v>7.8007</v>
       </c>
       <c r="X22" t="n">
-        <v>-7.461600000000001</v>
+        <v>-7.549799999999999</v>
       </c>
     </row>
   </sheetData>
